--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1995000</v>
+        <v>2142.93</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37285000</v>
+        <v>40049.63</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6400000</v>
+        <v>6874.55</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16065000</v>
+        <v>17256.2</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2600000</v>
+        <v>2792.79</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2447000</v>
+        <v>2628.44</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19348000</v>
+        <v>20782.62</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12348752</v>
+        <v>13264.39</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>377000</v>
+        <v>404.95</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3840000</v>
+        <v>4124.73</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27000000</v>
+        <v>29002.01</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12995200</v>
+        <v>13958.77</v>
       </c>
     </row>
     <row r="14">
@@ -1297,17 +1297,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11940000</v>
+        <v>12825.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1347,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>44786840</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1408,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>91000</v>
+        <v>48107.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>1134432-487-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,48 +1449,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t xml:space="preserve">FELIPE </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>798000</v>
+        <v>1879.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>4886-60-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,48 +1510,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9710400</v>
+        <v>857.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1134432-487-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1749500</v>
+        <v>10430.41</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5000000</v>
+        <v>5370.74</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>25440000</v>
+        <v>27326.34</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11500000</v>
+        <v>12352.71</v>
       </c>
     </row>
     <row r="23">
@@ -1846,17 +1846,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7980000</v>
+        <v>8571.700000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1057536-1747-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1896,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17880000</v>
+        <v>25715.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>1057536-1856-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,43 +1942,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>400000</v>
+        <v>37586.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057536-1856-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,43 +2003,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34992000</v>
+        <v>429.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057536-1747-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>23940000</v>
+        <v>19205.77</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>42840000</v>
+        <v>46016.52</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3500000</v>
+        <v>3759.52</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13000000</v>
+        <v>13963.93</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3268000</v>
+        <v>3510.32</v>
       </c>
     </row>
     <row r="32">
@@ -2395,17 +2395,17 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>200000</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4500000</v>
+        <v>193131.89</v>
       </c>
     </row>
     <row r="34">
@@ -2517,17 +2517,17 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>9000000</v>
+        <v>9667.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5965-193-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,48 +2547,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>606900</v>
+        <v>4833.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,43 +2613,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>179800000</v>
+        <v>12245.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2674,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11399991</v>
+        <v>32224.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,43 +2735,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>30000000</v>
+        <v>16112.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>2424-948-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2796,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>77.196.907-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15000000</v>
+        <v>14286.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2424-948-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2857,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.196.907-0</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13300000</v>
+        <v>5155.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,53 +2908,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4800000</v>
+        <v>64448.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>748-58-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>PATRICIO OSVALDO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>59999955</v>
+        <v>6015.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>748-58-CM26</t>
+          <t>748-59-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3066,17 +3066,17 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5600000</v>
+        <v>1278.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>748-59-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,37 +3101,37 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PATRICIO OSVALDO</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1190000</v>
+        <v>47933.88</v>
       </c>
     </row>
     <row r="45">
@@ -3188,17 +3188,17 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>134551</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>3134-146-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,37 +3223,37 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.854.171-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>44625000</v>
+        <v>5152.57</v>
       </c>
     </row>
     <row r="47">
@@ -3310,17 +3310,17 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>16900000</v>
+        <v>18153.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3134-146-CM26</t>
+          <t>4887-85-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3345,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.978.390-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>Subsecretaria de las Culturas y las Artes Region de la Araucania</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4796890</v>
+        <v>1278.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>2416-187-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,43 +3406,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6720000</v>
+        <v>46725.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4887-85-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,43 +3467,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.978.390-5</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Region de la Araucania</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1190000</v>
+        <v>7218.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2416-187-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,43 +3528,43 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>43500000</v>
+        <v>9357.610000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>2467-871-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,43 +3589,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8711657</v>
+        <v>526.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2467-871-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,43 +3650,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>490000</v>
+        <v>10182.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>2416-186-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,43 +3711,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9480000</v>
+        <v>44061.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2416-186-CM26</t>
+          <t>5952-97-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,43 +3772,43 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Hugo Pascual Paco Bolaños</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>10.472.608-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41020000</v>
+        <v>1074.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5952-97-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,43 +3833,43 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hugo Pascual Paco Bolaños</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10.472.608-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1000000</v>
+        <v>9183.969999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,43 +3894,43 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8550000</v>
+        <v>7680.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +3955,43 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7150472</v>
+        <v>1826.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>4886-97-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,28 +4031,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1700000</v>
+        <v>212.68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>2793-734-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,43 +4077,43 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>198000</v>
+        <v>6586.68</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2793-734-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,28 +4153,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6132000</v>
+        <v>11278.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,43 +4199,43 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>10500000</v>
+        <v>43412.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>2102-655-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,83 +4275,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.343.454-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>40416000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2102-655-CM26</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>61.602.212-1</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>76.343.454-0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>15340000</v>
+        <v>16477.44</v>
       </c>
     </row>
   </sheetData>
